--- a/JsonConverter/ExcelFiles/Stage.xlsx
+++ b/JsonConverter/ExcelFiles/Stage.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755AF109-8C62-4303-BE49-B161403D92EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D5E5A5D-6CB4-4755-8A80-32C3D3DEB363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -102,6 +102,10 @@
   </si>
   <si>
     <t>wave5_01,wave5_02,wave5_03,wave5_04,wave5_05,wave5_06,wave5_07,wave5_08</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -571,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>

--- a/JsonConverter/ExcelFiles/Stage.xlsx
+++ b/JsonConverter/ExcelFiles/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D5E5A5D-6CB4-4755-8A80-32C3D3DEB363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6824FB9-C065-4994-A88D-DCC9C6BA002D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -69,14 +69,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>시작 고기 수량</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartMeatCount</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>stage_04</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -106,6 +98,22 @@
   </si>
   <si>
     <t>string[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PrefabPath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 맵 프리팹 주소</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 시작 재화</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartGold</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -535,7 +543,7 @@
     <col min="2" max="2" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="88.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.5703125" style="2" customWidth="1"/>
     <col min="7" max="8" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="44.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -551,12 +559,14 @@
         <v>5</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -575,9 +585,11 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -593,12 +605,14 @@
         <v>6</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="14"/>
+      <c r="E3" s="14" t="s">
+        <v>19</v>
+      </c>
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
       <c r="H3" s="14"/>
@@ -617,7 +631,7 @@
         <v>200</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="8"/>
@@ -642,7 +656,7 @@
         <v>200</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -667,7 +681,7 @@
         <v>200</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -683,7 +697,7 @@
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -692,7 +706,7 @@
         <v>200</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -708,7 +722,7 @@
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5">
         <v>3</v>
@@ -717,7 +731,7 @@
         <v>200</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>

--- a/JsonConverter/ExcelFiles/Stage.xlsx
+++ b/JsonConverter/ExcelFiles/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6824FB9-C065-4994-A88D-DCC9C6BA002D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA297A78-F6A6-4195-95D1-D572E8FC521C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2220" yWindow="2700" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -43,10 +43,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>stage_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>stage별 목숨</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -55,12 +51,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>stage_02</t>
-  </si>
-  <si>
-    <t>stage_03</t>
-  </si>
-  <si>
     <t>wave Id</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -69,34 +59,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>stage_04</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>stage_05</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave1_01,wave1_02,wave1_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave2_01,wave2_02,wave2_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave3_01,wave3_02,wave3_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave4_01,wave4_02,wave4_03,wave4_04,wave4_05</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave5_01,wave5_02,wave5_03,wave5_04,wave5_05,wave5_06,wave5_07,wave5_08</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>string[]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -114,6 +76,62 @@
   </si>
   <si>
     <t>StartGold</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Stage/Stage_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Stage/Stage_02</t>
+  </si>
+  <si>
+    <t>Prefabs/Stage/Stage_03</t>
+  </si>
+  <si>
+    <t>Prefabs/Stage/Stage_04</t>
+  </si>
+  <si>
+    <t>Prefabs/Stage/Stage_05</t>
+  </si>
+  <si>
+    <t>Stage_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage_04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage_05</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave1_01,Wave1_02,Wave1_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_01,Wave2_02,Wave2_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_01,Wave3_02,Wave3_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave4_01,Wave4_02,Wave4_03,Wave4_04,Wave4_05</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave5_01,Wave5_02,Wave5_03,Wave5_04,Wave5_05,Wave5_06,Wave5_07,Wave5_08</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -556,16 +574,16 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -585,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>1</v>
@@ -602,16 +620,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
@@ -622,7 +640,7 @@
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -631,9 +649,11 @@
         <v>200</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="1"/>
       <c r="F4" s="8"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -647,7 +667,7 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B5" s="5">
         <v>3</v>
@@ -656,9 +676,11 @@
         <v>200</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -672,7 +694,7 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -681,9 +703,11 @@
         <v>200</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -697,7 +721,7 @@
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -706,9 +730,11 @@
         <v>200</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -722,7 +748,7 @@
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B8" s="5">
         <v>3</v>
@@ -731,9 +757,11 @@
         <v>200</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
